--- a/data/trans_bre/P13_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P13_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,74</t>
+          <t>-2,76; 3,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 18,69</t>
+          <t>8,11; 19,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 9,07</t>
+          <t>-0,24; 9,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,16</t>
+          <t>-2,51; 1,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,36; 250,93</t>
+          <t>-67,28; 244,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>112,69; 510,58</t>
+          <t>107,58; 536,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 242,84</t>
+          <t>-6,79; 244,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-84,49; 266,5</t>
+          <t>-89,29; 207,56</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,83</t>
+          <t>-1,07; 4,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 10,1</t>
+          <t>3,18; 9,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,56</t>
+          <t>-0,97; 3,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 6,2</t>
+          <t>0,58; 6,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 151,88</t>
+          <t>-17,63; 139,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,4; 331,31</t>
+          <t>46,58; 304,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 215,57</t>
+          <t>-29,34; 235,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 226,97</t>
+          <t>9,0; 251,06</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,28</t>
+          <t>-1,0; 3,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 7,11</t>
+          <t>0,78; 7,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,63</t>
+          <t>-2,52; 0,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 6,7</t>
+          <t>-0,72; 6,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-76,26; 1136,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 445,27</t>
+          <t>1,6; 415,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 344,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 124,66</t>
+          <t>-9,12; 116,4</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,22</t>
+          <t>-0,92; 3,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,93</t>
+          <t>3,63; 9,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 6,36</t>
+          <t>-0,67; 6,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 2,51</t>
+          <t>-4,62; 2,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 655,72</t>
+          <t>-65,17; 751,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,49; 740,92</t>
+          <t>85,29; 745,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 214,28</t>
+          <t>-18,12; 193,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,07; 56,6</t>
+          <t>-53,49; 65,99</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 8,28</t>
+          <t>-0,14; 8,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 13,91</t>
+          <t>4,07; 14,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 7,85</t>
+          <t>-0,54; 8,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,03</t>
+          <t>-2,34; 3,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 702,08</t>
+          <t>-14,95; 776,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,9; 985,78</t>
+          <t>61,69; 1042,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 417,32</t>
+          <t>-20,97; 431,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 109,29</t>
+          <t>-38,01; 114,36</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,23</t>
+          <t>0,71; 3,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,64</t>
+          <t>-1,91; 5,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 8,22</t>
+          <t>0,03; 8,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,52</t>
+          <t>0,8; 7,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 199,68</t>
+          <t>-35,05; 192,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 319,47</t>
+          <t>-4,26; 348,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 160,96</t>
+          <t>8,11; 178,74</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,64</t>
+          <t>-0,62; 4,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,54</t>
+          <t>0,92; 5,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,86</t>
+          <t>0,56; 5,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 3,32</t>
+          <t>-4,38; 3,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 136,23</t>
+          <t>-10,7; 135,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,9; 382,58</t>
+          <t>26,31; 387,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,94; 193,41</t>
+          <t>8,53; 212,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-55,65; 56,21</t>
+          <t>-52,14; 62,81</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,75</t>
+          <t>-0,88; 3,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,42</t>
+          <t>-1,59; 4,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,55</t>
+          <t>-1,21; 2,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,65</t>
+          <t>1,19; 6,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 104,42</t>
+          <t>-19,23; 109,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 60,78</t>
+          <t>-15,45; 56,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 131,68</t>
+          <t>-32,43; 125,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,32; 353,99</t>
+          <t>18,56; 300,92</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,56</t>
+          <t>0,74; 2,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,89</t>
+          <t>3,34; 5,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,12</t>
+          <t>1,03; 3,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,3</t>
+          <t>0,57; 3,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,35; 93,65</t>
+          <t>18,12; 96,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,16; 146,34</t>
+          <t>63,41; 143,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,09; 103,33</t>
+          <t>25,67; 101,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,92; 83,86</t>
+          <t>11,1; 85,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P13_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P13_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-27,14%</t>
+          <t>-22,46%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,58</t>
+          <t>-2,84; 3,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 19,12</t>
+          <t>7,76; 18,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 9,1</t>
+          <t>0,2; 9,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,07</t>
+          <t>-1,94; 0,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,28; 244,24</t>
+          <t>-64,62; 237,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>107,58; 536,74</t>
+          <t>108,71; 546,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 244,74</t>
+          <t>-0,5; 236,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-89,29; 207,56</t>
+          <t>-83,43; 212,89</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>3,24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,67</t>
+          <t>-1,02; 4,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,88</t>
+          <t>3,0; 10,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,41</t>
+          <t>-0,8; 3,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,29</t>
+          <t>0,19; 5,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 139,5</t>
+          <t>-16,89; 152,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,58; 304,12</t>
+          <t>46,16; 338,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,34; 235,4</t>
+          <t>-29,15; 276,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 251,06</t>
+          <t>0,93; 227,1</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,08</t>
+          <t>-1,03; 3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,4</t>
+          <t>0,34; 7,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,64</t>
+          <t>-2,42; 0,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 6,74</t>
+          <t>-0,3; 7,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>-70,35; 957,45</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-4,18; 508,8</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 415,53</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 344,93</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 116,4</t>
+          <t>-3,33; 133,84</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,47%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,36</t>
+          <t>-0,83; 3,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,99</t>
+          <t>3,68; 10,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 6,14</t>
+          <t>-0,59; 6,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,9</t>
+          <t>-2,28; 4,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,17; 751,26</t>
+          <t>-56,57; 812,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,29; 745,88</t>
+          <t>83,16; 753,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 193,57</t>
+          <t>-12,92; 202,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,49; 65,99</t>
+          <t>-29,14; 116,72</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 8,49</t>
+          <t>0,28; 8,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 14,08</t>
+          <t>3,41; 13,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 8,31</t>
+          <t>-0,44; 8,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,19</t>
+          <t>-2,14; 3,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 776,26</t>
+          <t>-8,55; 614,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,69; 1042,73</t>
+          <t>46,99; 1005,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 431,69</t>
+          <t>-19,58; 393,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 114,36</t>
+          <t>-37,13; 142,51</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>64,89%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,92</t>
+          <t>0,71; 4,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,52</t>
+          <t>-2,11; 5,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 8,1</t>
+          <t>-0,43; 8,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,03</t>
+          <t>0,28; 6,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 192,33</t>
+          <t>-36,49; 190,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 348,83</t>
+          <t>-13,33; 357,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 178,74</t>
+          <t>-0,53; 164,99</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,52</t>
+          <t>-0,68; 4,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,32</t>
+          <t>0,94; 5,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,93</t>
+          <t>0,64; 6,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 3,53</t>
+          <t>-0,69; 4,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 135,57</t>
+          <t>-13,68; 143,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,31; 387,36</t>
+          <t>22,57; 398,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,53; 212,63</t>
+          <t>12,02; 211,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 62,81</t>
+          <t>-9,53; 81,68</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,51</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,73</t>
+          <t>-0,79; 3,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,27</t>
+          <t>-2,05; 4,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,7</t>
+          <t>-1,0; 2,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,54</t>
+          <t>0,33; 4,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 109,62</t>
+          <t>-16,08; 110,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 56,15</t>
+          <t>-19,61; 58,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,43; 125,91</t>
+          <t>-28,66; 127,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,56; 300,92</t>
+          <t>4,53; 109,12</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,69</t>
+          <t>0,58; 2,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,95</t>
+          <t>3,53; 5,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,12</t>
+          <t>1,05; 3,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,37</t>
+          <t>1,12; 3,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,12; 96,14</t>
+          <t>15,73; 94,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,41; 143,83</t>
+          <t>68,32; 146,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,67; 101,19</t>
+          <t>26,24; 105,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,1; 85,35</t>
+          <t>19,21; 70,13</t>
         </is>
       </c>
     </row>
